--- a/public/downloads/remote-access-register.xlsx
+++ b/public/downloads/remote-access-register.xlsx
@@ -11,6 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Register!$A$1:$L$501</definedName>
   </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -38,8 +39,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7C2D12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -52,8 +73,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F1EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -76,11 +109,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD6D3CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD6D3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD6D3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD6D3CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -89,6 +137,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -102,80 +170,79 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1" style="2"/>
-    <col min="11" max="11" width="14" customWidth="1" style="2"/>
+    <col min="11" max="11" width="16" customWidth="1" style="2"/>
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" t="inlineStr" s="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Path ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Supplier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Site</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Method</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Account type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Second factor</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Scope</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant-side owner</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Supplier-side owner</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Expiry or end date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Last reviewed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Evidence location</t>
         </is>
@@ -184,22 +251,22 @@
   </sheetData>
   <autoFilter ref="A1:L501"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Method" error="Choose one of: VPN, Remote support tool, Jump host, Cloud broker, OT gateway, Modem, Other." sqref="D2:D501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose from the list" error="Choose one of: VPN, Remote support tool, Jump host, Cloud broker, OT gateway, Modem, Other." sqref="D2:D501">
       <formula1>"VPN,Remote support tool,Jump host,Cloud broker,OT gateway,Modem,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Account type" error="Choose one of: Named, Shared." sqref="E2:E501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose from the list" error="Choose one of: Named, Shared." sqref="E2:E501">
       <formula1>"Named,Shared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Second factor" error="Choose one of: Y, N." sqref="F2:F501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose from the list" error="Choose one of: Y, N." sqref="F2:F501">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Scope" error="Choose one of: Single machine, Cell or line, Network segment, Whole site, Unknown." sqref="G2:G501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose from the list" error="Choose one of: Single machine, Cell or line, Network segment, Whole site, Unknown." sqref="G2:G501">
       <formula1>"Single machine,Cell or line,Network segment,Whole site,Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Expiry or end date" error="Enter a date, for example 2027-03-31." sqref="J2:J501">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Date" error="Enter a date, for example 2027-03-31." sqref="J2:J501">
       <formula1>36526</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Last reviewed" error="Enter a date, for example 2027-03-31." sqref="K2:K501">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Date" error="Enter a date, for example 2027-03-31." sqref="K2:K501">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -210,6 +277,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -218,269 +288,270 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="3">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Remote access register</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">One row per remote access path: one supplier reaching one site by one method.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One row per remote access path: one supplier reaching one site by one method. It is the deliverable of the first step of the 90-day plan, and the first thing to hand over when a customer, an auditor or management asks how remote access is governed.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr" s="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">A row without two named owners, or without an end date, is the first thing to fix.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr" s="4">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">A shared account or a missing second factor needs a dated exception with a reason.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="4">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Review every row at least as often as you review supplier access in general, and record the date.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr" s="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Column</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="1">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What to record</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="1">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Allowed values</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr" s="3">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Path ID</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="4">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Your own reference, unique per row.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="4">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="3">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Supplier</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="4">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">The company whose people connect. Write in a dealer or subcontractor as its own row.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="4">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr" s="3">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Site</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="4">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">The plant or location reached.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="4">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr" s="3">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Method</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="4">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">How the connection is made.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="4">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">VPN, Remote support tool, Jump host, Cloud broker, OT gateway, Modem, Other</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr" s="3">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Account type</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="4">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Whether each person has their own login.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="4">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Named, Shared</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr" s="3">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Second factor</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="4">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Whether a second factor is enforced on this path.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="4">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Y, N</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr" s="3">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scope</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="4">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">What a session can reach.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="4">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Single machine, Cell or line, Network segment, Whole site, Unknown</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr" s="3">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant-side owner</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="4">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">The named person at the plant responsible for this path.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="4">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr" s="3">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Supplier-side owner</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="4">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">The named person at the supplier responsible for this path.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="4">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr" s="3">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Expiry or end date</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="4">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">When access ends unless renewed. A date, never blank.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr" s="4">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">A date</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="3">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Last reviewed</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr" s="4">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">When someone last confirmed the row is still true.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="4">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">A date</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr" s="3">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Evidence location</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr" s="4">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Where the proof is: configuration export, account list, log store.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="4">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr" s="4">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">From the regional report Remote Access Is a Governance Problem, Appendix B. Software Lantern. A general template, not legal or security advice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>